--- a/input/mapping/038. OCB_GOLD_TCKH_V_SECTOR_LIST_HOP.xlsx
+++ b/input/mapping/038. OCB_GOLD_TCKH_V_SECTOR_LIST_HOP.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D19A884-F608-4937-8687-3130942EC448}"/>
+  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DF9B0D-87F7-44D3-AF1B-DE0288F174C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Script" sheetId="3" r:id="rId2"/>
     <sheet name="SECTOR_LIST" sheetId="2" state="hidden" r:id="rId3"/>
-    <sheet name="V_SECTOR_LIST" sheetId="4" r:id="rId4"/>
+    <sheet name="V_SECTOR_LIST" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028" iterateDelta="1E-4" calcOnSave="0"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
   <si>
     <t xml:space="preserve">V_SECTOR_LIST  —  Data Lineage </t>
   </si>
@@ -183,6 +183,9 @@
     <t>SECTOR_NAME</t>
   </si>
   <si>
+    <t xml:space="preserve">JOIN SCHEMA — LV1  </t>
+  </si>
+  <si>
     <t>ON Condition / Ghi chú</t>
   </si>
   <si>
@@ -192,60 +195,13 @@
     <t>Target View</t>
   </si>
   <si>
-    <t>Field</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
     <t>1-1</t>
   </si>
   <si>
-    <t>OCBDW2.CV.CL_ID</t>
-  </si>
-  <si>
-    <t>OCBDW2.CV</t>
-  </si>
-  <si>
-    <t>Key SOR tự sinh</t>
-  </si>
-  <si>
-    <t>T24_sector</t>
-  </si>
-  <si>
     <t>Ref_hashkey</t>
   </si>
   <si>
-    <t>OCBDW2.CV.SRC_CL_ID AS SECTOR
-(mã ngành nghề — VD: 'AGRI', 'BANK'...)</t>
-  </si>
-  <si>
-    <t>SRC_CL_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1:01
-</t>
-  </si>
-  <si>
-    <t>t24_sector.ID</t>
-  </si>
-  <si>
     <t>Ref_code</t>
-  </si>
-  <si>
-    <t>OCBDW2.CV.DSC_VIET AS SECTOR_NAME
-(tên ngành nghề tiếng Việt)</t>
-  </si>
-  <si>
-    <t>DSC_VIET</t>
-  </si>
-  <si>
-    <t>substring_by_delimiter(
-  T_DESCRIPTION, '::', 2)</t>
-  </si>
-  <si>
-    <t>t24_sector.T_DESCRIPTION
-(format 'ENG::VIET')</t>
   </si>
   <si>
     <t xml:space="preserve">   CASE
@@ -259,14 +215,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,8 +346,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF546E7A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,8 +439,14 @@
         <fgColor rgb="FF1A1A6E"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -610,19 +593,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -633,28 +660,19 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -672,49 +690,62 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
@@ -725,28 +756,37 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1089,128 +1129,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="45"/>
-      <c r="L1" s="45"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
     </row>
     <row r="2" spans="1:24" ht="21.95" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="46" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
-      <c r="M3" s="44"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
+      <c r="A5" s="55"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
     </row>
     <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
     </row>
     <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="37"/>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44"/>
+      <c r="A7" s="55"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
     </row>
     <row r="8" spans="1:24" ht="18" customHeight="1"/>
     <row r="9" spans="1:24" ht="18" customHeight="1">
@@ -1224,63 +1264,63 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:24" ht="18" customHeight="1">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49"/>
-      <c r="E11" s="50"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="54"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:24" ht="18" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="45"/>
     </row>
     <row r="13" spans="1:24" ht="18" customHeight="1">
       <c r="A13" s="6"/>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="43"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="45"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:24" ht="18" customHeight="1">
       <c r="A14" s="7"/>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="43"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="45"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:24" ht="18" customHeight="1">
       <c r="A15" s="8"/>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="43"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="45"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:24" ht="18" customHeight="1">
       <c r="A16" s="9"/>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="43"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="45"/>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1">
       <c r="G17" s="3"/>
@@ -1296,10 +1336,10 @@
       <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="18" customHeight="1">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="36" t="s">
+      <c r="B19" s="32" t="s">
         <v>11</v>
       </c>
       <c r="G19" s="3"/>
@@ -1308,10 +1348,10 @@
       <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="18" customHeight="1">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="16" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1333,70 +1373,70 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="40"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="40"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="40"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
     </row>
     <row r="29" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="51"/>
+      <c r="H29" s="51"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
     </row>
     <row r="30" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B30" s="39"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="47"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="51"/>
+      <c r="H30" s="51"/>
+      <c r="I30" s="51"/>
+      <c r="J30" s="51"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
     </row>
     <row r="32" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="47"/>
-      <c r="H32" s="47"/>
-      <c r="I32" s="47"/>
-      <c r="J32" s="47"/>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
     </row>
     <row r="33" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="38"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="47"/>
-      <c r="H33" s="47"/>
-      <c r="I33" s="47"/>
-      <c r="J33" s="47"/>
+      <c r="B33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
     </row>
     <row r="34" spans="2:10" ht="18" customHeight="1"/>
   </sheetData>
@@ -1423,12 +1463,12 @@
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="H2:M7"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B15:E15"/>
-    <mergeCell ref="H2:M7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1446,16 +1486,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="26" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1470,14 +1510,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="409.6">
       <c r="A3" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="4" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1502,30 +1542,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="24" t="s">
         <v>27</v>
       </c>
       <c r="F2" s="10"/>
@@ -1558,36 +1598,36 @@
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="56"/>
+      <c r="D5" s="56"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="24" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1661,13 +1701,13 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1680,288 +1720,147 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F86CFC7-3335-4071-A22A-698EF6FB7C61}">
-  <dimension ref="A1:M10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8952EF9-E034-4864-AA2E-A5B7434F544F}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="17"/>
-    <col min="2" max="2" width="26.42578125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" style="15" customWidth="1"/>
-    <col min="5" max="5" width="50.85546875" style="15" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" style="15" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5703125" style="15" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="15" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="24.85546875" style="15" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="28" style="15" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="15" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="51.140625" style="15" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="15"/>
+    <col min="1" max="1" width="9.140625" style="20"/>
+    <col min="2" max="2" width="26.42578125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" style="21" customWidth="1"/>
+    <col min="5" max="5" width="46.42578125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="49.42578125" style="21" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1">
-      <c r="A1" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="26" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="12">
+      <c r="E2" s="34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="35">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="37"/>
+      <c r="D3" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-    </row>
-    <row r="4" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-    </row>
-    <row r="5" spans="1:13" ht="13.5" customHeight="1">
-      <c r="A5" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="24"/>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1">
-      <c r="A6" s="30" t="s">
+      <c r="E3" s="39"/>
+    </row>
+    <row r="4" spans="1:6" ht="15" customHeight="1">
+      <c r="A4" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="B5" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E5" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F5" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="32" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="15">
+        <v>1</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16.5" customHeight="1">
+      <c r="A7" s="15">
+        <v>2</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="86.25" customHeight="1">
+      <c r="A8" s="15">
+        <v>3</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="J6" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="M6" s="24"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="16">
-        <v>1</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="16" t="s">
+      <c r="F8" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="L7" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="24"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="16">
-        <v>2</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H8" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="M8" s="24"/>
-    </row>
-    <row r="9" spans="1:13" ht="81.75" customHeight="1">
-      <c r="A9" s="16">
-        <v>3</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="M9" s="24"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1973,6 +1872,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1981,7 +1890,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2153,24 +2062,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C9CD0F-F06A-4CB4-AECA-A7F437F3D1E1}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DAAA06A-7575-4AEE-A357-AE598CC1F868}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
 </file>
--- a/input/mapping/038. OCB_GOLD_TCKH_V_SECTOR_LIST_HOP.xlsx
+++ b/input/mapping/038. OCB_GOLD_TCKH_V_SECTOR_LIST_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/HOP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="495" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27DF9B0D-87F7-44D3-AF1B-DE0288F174C5}"/>
+  <xr:revisionPtr revIDLastSave="499" documentId="13_ncr:1_{82C45277-8561-4971-BEC1-8042A5E437B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1355567-B8FF-400D-921D-A1BCFE7D454B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -117,7 +117,7 @@
             THEN TRIM(SPLIT_PART(Ref_description, '::', 2))
         ELSE TRIM(Ref_description)
     END                                                     AS SECTOR_NAME
-FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector');</t>
+FROM IDENTIFIER(:cleaned || '.raw_vault.ref_t24_sector')</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -641,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -738,56 +738,59 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1129,21 +1132,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="30" customHeight="1">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
-      <c r="M1" s="49"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
       <c r="N1" s="31"/>
       <c r="O1" s="31"/>
       <c r="P1" s="31"/>
@@ -1157,100 +1160,100 @@
       <c r="X1" s="31"/>
     </row>
     <row r="2" spans="1:24" ht="21.95" customHeight="1">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="50" t="s">
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="55"/>
-      <c r="B4" s="55"/>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
     </row>
     <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="50"/>
     </row>
     <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="50"/>
     </row>
     <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="55"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
+      <c r="A7" s="48"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
     </row>
     <row r="8" spans="1:24" ht="18" customHeight="1"/>
     <row r="9" spans="1:24" ht="18" customHeight="1">
@@ -1264,63 +1267,63 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:24" ht="18" customHeight="1">
-      <c r="A11" s="52" t="s">
+      <c r="A11" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="54"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="47"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:24" ht="18" customHeight="1">
       <c r="A12" s="5"/>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="45"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="53"/>
     </row>
     <row r="13" spans="1:24" ht="18" customHeight="1">
       <c r="A13" s="6"/>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="45"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="53"/>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:24" ht="18" customHeight="1">
       <c r="A14" s="7"/>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="45"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="53"/>
       <c r="F14" s="1"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:24" ht="18" customHeight="1">
       <c r="A15" s="8"/>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="44"/>
-      <c r="D15" s="44"/>
-      <c r="E15" s="45"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="53"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:24" ht="18" customHeight="1">
       <c r="A16" s="9"/>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="45"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="53"/>
     </row>
     <row r="17" spans="1:10" ht="18" customHeight="1">
       <c r="G17" s="3"/>
@@ -1373,74 +1376,86 @@
       <c r="J27" s="2"/>
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1">
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
     </row>
     <row r="29" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B29" s="47"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="47"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="51"/>
-      <c r="H29" s="51"/>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="43"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
     </row>
     <row r="30" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B30" s="47"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="47"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="51"/>
-      <c r="H30" s="51"/>
-      <c r="I30" s="51"/>
-      <c r="J30" s="51"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="43"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
     </row>
     <row r="31" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="46"/>
-      <c r="F31" s="46"/>
-      <c r="G31" s="51"/>
-      <c r="H31" s="51"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
     </row>
     <row r="32" spans="1:10" ht="27.95" customHeight="1">
-      <c r="B32" s="47"/>
-      <c r="C32" s="47"/>
-      <c r="D32" s="47"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="46"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="51"/>
-      <c r="J32" s="51"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
     </row>
     <row r="33" spans="2:10" ht="27.95" customHeight="1">
-      <c r="B33" s="47"/>
-      <c r="C33" s="47"/>
-      <c r="D33" s="47"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="51"/>
-      <c r="J33" s="51"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="44"/>
+      <c r="G33" s="43"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
     </row>
     <row r="34" spans="2:10" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="H2:M7"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="G2:G7"/>
     <mergeCell ref="B33:D33"/>
@@ -1457,18 +1472,6 @@
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="A11:E11"/>
     <mergeCell ref="A2:F7"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="H2:M7"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B15:E15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1482,7 +1485,7 @@
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
     <col min="3" max="3" width="24.140625" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1510,14 +1513,14 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="57" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1542,13 +1545,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
     </row>
@@ -1598,15 +1601,15 @@
       <c r="G4" s="10"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="56"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="56"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="23" t="s">
@@ -1734,13 +1737,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="34" t="s">
@@ -1872,25 +1875,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -2062,8 +2046,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DAAA06A-7575-4AEE-A357-AE598CC1F868}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2071,5 +2074,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DAAA06A-7575-4AEE-A357-AE598CC1F868}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05B676A7-3FE0-4AFA-BF95-5F9A645EA2A6}"/>
 </file>